--- a/Assets/Resources/NpcQuestDataBase.xlsx
+++ b/Assets/Resources/NpcQuestDataBase.xlsx
@@ -13,6 +13,7 @@
   </bookViews>
   <sheets>
     <sheet name="NpcQuestDataBase" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -1242,9 +1243,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE7"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.25" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="9.625" bestFit="1" customWidth="1"/>
     <col min="19" max="20" width="23.5" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="11.625" bestFit="1" customWidth="1"/>
@@ -1260,7 +1275,7 @@
     <col min="31" max="31" width="15.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1303,11 +1318,8 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="R1" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="2" spans="1:31" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -1335,50 +1347,8 @@
       <c r="J2">
         <v>1</v>
       </c>
-      <c r="R2" t="s">
-        <v>19</v>
-      </c>
-      <c r="S2" t="s">
-        <v>19</v>
-      </c>
-      <c r="T2" t="s">
-        <v>19</v>
-      </c>
-      <c r="U2" t="s">
-        <v>19</v>
-      </c>
-      <c r="V2" t="s">
-        <v>19</v>
-      </c>
-      <c r="W2" t="s">
-        <v>20</v>
-      </c>
-      <c r="X2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>22</v>
-      </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -1415,50 +1385,8 @@
       <c r="L3">
         <v>1</v>
       </c>
-      <c r="R3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="U3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="Y3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="Z3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE3" s="4" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -1483,106 +1411,212 @@
       <c r="H4">
         <v>100</v>
       </c>
-      <c r="R4" s="5" t="s">
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="T4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="U4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="X4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Z4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AA4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AB4" s="1"/>
-      <c r="AC4" s="1"/>
-      <c r="AD4" s="1"/>
-      <c r="AE4" s="6"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="6"/>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="R5" s="5"/>
-      <c r="S5" s="1"/>
-      <c r="T5" s="1"/>
-      <c r="U5" s="1" t="s">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="5"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="V5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="W5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="X5" s="1"/>
-      <c r="Y5" s="1"/>
-      <c r="Z5" s="1"/>
-      <c r="AA5" s="1"/>
-      <c r="AB5" s="1"/>
-      <c r="AC5" s="1"/>
-      <c r="AD5" s="1"/>
-      <c r="AE5" s="6"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="6"/>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="R6" s="5"/>
-      <c r="S6" s="1"/>
-      <c r="T6" s="1"/>
-      <c r="U6" s="1" t="s">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="5"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="V6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="W6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="X6" s="1"/>
-      <c r="Y6" s="1"/>
-      <c r="Z6" s="1"/>
-      <c r="AA6" s="1"/>
-      <c r="AB6" s="1"/>
-      <c r="AC6" s="1"/>
-      <c r="AD6" s="1"/>
-      <c r="AE6" s="6"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="6"/>
     </row>
-    <row r="7" spans="1:31" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="R7" s="7"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
-      <c r="U7" s="8" t="s">
+    <row r="7" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="7"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="V7" s="8" t="s">
+      <c r="E7" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="W7" s="8" t="s">
+      <c r="F7" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="X7" s="8"/>
-      <c r="Y7" s="8"/>
-      <c r="Z7" s="8"/>
-      <c r="AA7" s="8"/>
-      <c r="AB7" s="8"/>
-      <c r="AC7" s="8"/>
-      <c r="AD7" s="8"/>
-      <c r="AE7" s="9"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>

--- a/Assets/Resources/NpcQuestDataBase.xlsx
+++ b/Assets/Resources/NpcQuestDataBase.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\SangDol\Assets\Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\SangDol\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{347BF737-5127-46C0-954C-EFFC9A43C432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11475"/>
+    <workbookView xWindow="3480" yWindow="4620" windowWidth="19905" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NpcQuestDataBase" sheetId="1" r:id="rId1"/>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="49">
   <si>
     <t>Quest_ID</t>
   </si>
@@ -70,12 +71,6 @@
     <t>Q_30001_001</t>
   </si>
   <si>
-    <t>배달</t>
-  </si>
-  <si>
-    <t>퀘스트 설명_Q_30001_001</t>
-  </si>
-  <si>
     <t>Talk</t>
   </si>
   <si>
@@ -164,12 +159,24 @@
   </si>
   <si>
     <t>아이템 목표 개수</t>
+  </si>
+  <si>
+    <t>모험의 시작</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>눈을 뜨니까 처음 보는 마을이다. 마리아에게 가보자.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quest_ClearNpcID</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1242,40 +1249,41 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="20.625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1286,129 +1294,129 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>15</v>
       </c>
       <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2">
+        <v>30002</v>
+      </c>
+      <c r="E2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2">
-        <v>30001</v>
-      </c>
-      <c r="G2">
-        <v>100</v>
+      <c r="F2">
+        <v>30002</v>
       </c>
       <c r="H2">
         <v>100</v>
       </c>
       <c r="I2">
-        <v>10001</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
         <v>23</v>
       </c>
-      <c r="B3" t="s">
+      <c r="E3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" t="s">
+      <c r="F3" t="s">
         <v>25</v>
       </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3">
+      <c r="G3">
         <v>5</v>
-      </c>
-      <c r="G3">
-        <v>100</v>
       </c>
       <c r="H3">
         <v>100</v>
       </c>
       <c r="I3">
+        <v>100</v>
+      </c>
+      <c r="J3">
         <v>10002</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>1</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>10003</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
         <v>28</v>
       </c>
-      <c r="B4" t="s">
+      <c r="E4" t="s">
         <v>29</v>
       </c>
-      <c r="C4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4">
+      <c r="F4">
         <v>20001</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>5</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>100</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>100</v>
       </c>
     </row>
@@ -1419,7 +1427,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -1430,46 +1438,46 @@
     </row>
     <row r="2" spans="1:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" t="s">
         <v>19</v>
       </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
         <v>20</v>
       </c>
-      <c r="G2" t="s">
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" t="s">
         <v>20</v>
       </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" t="s">
-        <v>22</v>
-      </c>
       <c r="M2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -1518,34 +1526,34 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -1557,13 +1565,13 @@
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -1579,13 +1587,13 @@
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -1601,13 +1609,13 @@
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>

--- a/Assets/Resources/NpcQuestDataBase.xlsx
+++ b/Assets/Resources/NpcQuestDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\SangDol\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{347BF737-5127-46C0-954C-EFFC9A43C432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9217AF42-8210-4DB7-A5CF-1AD2C2E48444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3480" yWindow="4620" windowWidth="19905" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NpcQuestDataBase" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="53">
   <si>
     <t>Quest_ID</t>
   </si>
@@ -170,6 +170,22 @@
   </si>
   <si>
     <t>Quest_ClearNpcID</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quest_TargetName</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>마리아</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>슬라임</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1250,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.75" bestFit="1" customWidth="1"/>
@@ -1260,30 +1276,31 @@
     <col min="5" max="5" width="11.375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="20.625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="15.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1306,31 +1323,34 @@
         <v>5</v>
       </c>
       <c r="H1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -1349,14 +1369,17 @@
       <c r="F2">
         <v>30002</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2">
         <v>100</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -1375,26 +1398,29 @@
       <c r="G3">
         <v>5</v>
       </c>
-      <c r="H3">
-        <v>100</v>
+      <c r="H3" t="s">
+        <v>51</v>
       </c>
       <c r="I3">
         <v>100</v>
       </c>
       <c r="J3">
+        <v>100</v>
+      </c>
+      <c r="K3">
         <v>10002</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>1</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>10003</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -1413,10 +1439,13 @@
       <c r="G4">
         <v>5</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4">
         <v>100</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>100</v>
       </c>
     </row>

--- a/Assets/Resources/NpcQuestDataBase.xlsx
+++ b/Assets/Resources/NpcQuestDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\SangDol\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9217AF42-8210-4DB7-A5CF-1AD2C2E48444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2713BF1A-E01D-4ADE-9590-1748CFF16EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7005" yWindow="2115" windowWidth="19845" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NpcQuestDataBase" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="54">
   <si>
     <t>Quest_ID</t>
   </si>
@@ -86,28 +86,7 @@
     <t>int</t>
   </si>
   <si>
-    <t>Q_30001_002</t>
-  </si>
-  <si>
-    <t>슬라임 토벌</t>
-  </si>
-  <si>
-    <t>퀘스트 설명_Q_30001_002</t>
-  </si>
-  <si>
     <t>Kill</t>
-  </si>
-  <si>
-    <t>Slime</t>
-  </si>
-  <si>
-    <t>Q_30001_003</t>
-  </si>
-  <si>
-    <t>식량 모으기</t>
-  </si>
-  <si>
-    <t>퀘스트 설명_Q_30001_003</t>
   </si>
   <si>
     <t>Item</t>
@@ -181,11 +160,42 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>슬라임</t>
+    <t>제철 사과</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>테스트</t>
+    <t>상인에게 '잘 익은 사과' 1개를 구입해, 마리아에게 주자.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>잘 익은 사과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Q_30001_002</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Q_30001_003</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>늑대 사냥</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>다일을 도와 마을 주변의 늑대를 5마리 처치하자.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kill</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wolf</t>
+  </si>
+  <si>
+    <t>늑대</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1311,7 +1321,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -1323,7 +1333,7 @@
         <v>5</v>
       </c>
       <c r="H1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="I1" t="s">
         <v>6</v>
@@ -1355,10 +1365,10 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D2">
         <v>30002</v>
@@ -1370,7 +1380,7 @@
         <v>30002</v>
       </c>
       <c r="H2" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="I2">
         <v>100</v>
@@ -1381,72 +1391,78 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3">
+        <v>30002</v>
+      </c>
+      <c r="E3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" t="s">
-        <v>25</v>
+      <c r="F3">
+        <v>20008</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="I3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K3">
-        <v>10002</v>
+        <v>20001</v>
       </c>
       <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>10003</v>
-      </c>
-      <c r="N3">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>50</v>
+      </c>
+      <c r="D4">
+        <v>30004</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4">
-        <v>20001</v>
+        <v>51</v>
+      </c>
+      <c r="F4" t="s">
+        <v>52</v>
       </c>
       <c r="G4">
         <v>5</v>
       </c>
       <c r="H4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I4">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>400</v>
+      </c>
+      <c r="K4">
+        <v>10008</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1555,34 +1571,34 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -1597,10 +1613,10 @@
         <v>16</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -1616,13 +1632,13 @@
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -1638,13 +1654,13 @@
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
